--- a/00.StartCamp_6team_project/docs/03_3일차_팀프로젝트_실습기획서_SeoulMySoulMate_완성본.xlsx
+++ b/00.StartCamp_6team_project/docs/03_3일차_팀프로젝트_실습기획서_SeoulMySoulMate_완성본.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\StartCamp\team_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A66036-907B-48F4-A4CE-8ED8FF7DA0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604A28E4-9141-4DC8-8417-AFA048E9DD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -4481,9 +4481,6 @@
     <t>서울 관광정보가 유형별로 흩어져 있고 실제 방문자의 후기와 함께 비교하거나 개인 일정으로 정리하기 어려움</t>
   </si>
   <si>
-    <t>서울 여행을 준비하는 관광객, 주말 나들이 장소를 찾는 서울 시민, 회원가입 없이 정보를 공유하려는 이용자</t>
-  </si>
-  <si>
     <t>팀전체</t>
   </si>
   <si>
@@ -5216,9 +5213,6 @@
     <t>SeoulMySoulMate MVP 정의서 (구현 현황 반영)</t>
   </si>
   <si>
-    <t>서울 관광 데이터 7종 6,518건 적재, 회원 커뮤니티 CRUD·Soul Chat·플래너·지도·실시간 정보 구현, 프론트 빌드와 핵심 API 스모크 테스트 통과</t>
-  </si>
-  <si>
     <t>Must have (현재 구현 완료)</t>
   </si>
   <si>
@@ -5234,19 +5228,7 @@
     <t>Vue 3 SPA와 FastAPI REST API 연동, 콘텐츠·지도·인증·커뮤니티·챗봇·플래너 화면 및 반응형 상태 UI 구현</t>
   </si>
   <si>
-    <t>비밀번호·세션 토큰 해시 저장, API 키 환경변수 관리, 외부 API 누락·실패에 대한 폴백과 캐시 처리</t>
-  </si>
-  <si>
     <t>Should / Could have (선정·구현 완료)</t>
-  </si>
-  <si>
-    <t>서버 저장 서울 여행 플래너 - 날짜·방문시간·메모·순서·날짜 변경 및 삭제</t>
-  </si>
-  <si>
-    <t>전체 장소 지도 - 카카오맵 마커 클러스터, 카테고리·지역·키워드 필터와 상세 연결</t>
-  </si>
-  <si>
-    <t>실시간 혼잡도·따릉이·상권 정보와 라이트/다크 테마·온보딩·사이트 음악</t>
   </si>
   <si>
     <t>Won't have (이번 범위에서 제외 또는 후속 작업)</t>
@@ -5331,703 +5313,6 @@
   </si>
   <si>
     <r>
-      <t>사용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>경험을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>생각해서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>진행했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">….  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>챗봇에서도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>검색</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>결과에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>캘린더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>당장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>싶을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있어서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>혼잡도도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보여줌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자치구에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>혼잡도를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보여줘서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>여행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>목적에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맞는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>적절하게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선택할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>플랜을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>짜는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>과정을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자연스럽게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이어나갈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>고민을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>많이했습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>주요</t>
     </r>
     <r>
@@ -8838,6 +8123,2283 @@
         <charset val="129"/>
       </rPr>
       <t>제외</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여행을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광객</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찾는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시민</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원가입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공유하려는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이용자</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 6,518</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>커뮤니티</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CRUD·Soul Chat·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플래너</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프론트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빌드와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>핵심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스모크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통과</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비밀번호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>토큰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>환경변수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외부</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누락</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실패에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>폴백과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>캐시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처리</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서버</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플래너</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방문시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메모</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>삭제</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카카오맵</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>클러스터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카테고리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키워드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필터와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혼잡도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따릉이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상권</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라이트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온보딩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사이트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>음악</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경험을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생각해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진행했다…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>챗봇에서도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결과에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>캘린더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있어서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혼잡도도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보여줌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자치구에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혼잡도를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보여줘서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목적에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맞는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적절하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선택할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>했다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플랜을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짜는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과정을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자연스럽게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이어나갈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고민을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많이했습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>.</t>
     </r>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -8851,7 +10413,7 @@
     <numFmt numFmtId="177" formatCode=";;;"/>
     <numFmt numFmtId="178" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9157,6 +10719,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -9367,7 +10936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -9645,6 +11214,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -9908,7 +11480,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
       <c r="B2" s="52" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C2" s="52"/>
     </row>
@@ -9925,7 +11497,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="19.5" customHeight="1">
@@ -9946,7 +11518,7 @@
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
       <c r="B9" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C9" s="49"/>
     </row>
@@ -9963,7 +11535,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="33.75" customHeight="1">
@@ -9971,7 +11543,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="33.75" customHeight="1">
@@ -9979,7 +11551,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="33.75" customHeight="1">
@@ -9987,7 +11559,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="33.75" customHeight="1">
@@ -10223,7 +11795,7 @@
   <sheetData>
     <row r="2" spans="2:11" ht="30" customHeight="1">
       <c r="B2" s="60" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="58"/>
       <c r="D2" s="58"/>
@@ -10232,7 +11804,7 @@
     </row>
     <row r="3" spans="2:11" ht="28.35" customHeight="1">
       <c r="B3" s="61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="62"/>
@@ -10250,10 +11822,10 @@
         <v>53</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="66" customHeight="1">
@@ -10261,16 +11833,16 @@
         <v>119</v>
       </c>
       <c r="C5" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="E5" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="F5" s="27" t="s">
         <v>165</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="66" customHeight="1">
@@ -10278,16 +11850,16 @@
         <v>119</v>
       </c>
       <c r="C6" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="E6" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="F6" s="27" t="s">
         <v>169</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="66" customHeight="1">
@@ -10295,19 +11867,19 @@
         <v>119</v>
       </c>
       <c r="C7" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="E7" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="F7" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="F7" s="27" t="s">
-        <v>174</v>
-      </c>
       <c r="K7" s="98" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="66" customHeight="1">
@@ -10315,19 +11887,19 @@
         <v>119</v>
       </c>
       <c r="C8" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>175</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>176</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>120</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K8" s="98" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="66" customHeight="1">
@@ -10335,19 +11907,19 @@
         <v>119</v>
       </c>
       <c r="C9" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>178</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>179</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>121</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K9" s="98" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="66" customHeight="1">
@@ -10355,19 +11927,19 @@
         <v>123</v>
       </c>
       <c r="C10" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="E10" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="F10" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="F10" s="27" t="s">
-        <v>184</v>
-      </c>
       <c r="K10" s="98" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="2:11" ht="66" customHeight="1">
@@ -10375,19 +11947,19 @@
         <v>119</v>
       </c>
       <c r="C11" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="27" t="s">
         <v>185</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>186</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>122</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K11" s="98" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="66" customHeight="1">
@@ -10395,19 +11967,19 @@
         <v>126</v>
       </c>
       <c r="C12" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="E12" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="F12" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="F12" s="27" t="s">
-        <v>191</v>
-      </c>
       <c r="K12" s="98" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="2:11" ht="66" customHeight="1">
@@ -10415,19 +11987,19 @@
         <v>126</v>
       </c>
       <c r="C13" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="E13" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="F13" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="F13" s="27" t="s">
-        <v>195</v>
-      </c>
       <c r="K13" s="98" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="66" customHeight="1">
@@ -10435,16 +12007,16 @@
         <v>126</v>
       </c>
       <c r="C14" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="27" t="s">
         <v>196</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>197</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>127</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="66" customHeight="1">
@@ -10452,16 +12024,16 @@
         <v>124</v>
       </c>
       <c r="C15" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>125</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="66" customHeight="1">
@@ -10472,13 +12044,13 @@
         <v>129</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>130</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1"/>
@@ -10521,7 +12093,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
       <c r="B2" s="57" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C2" s="58"/>
       <c r="D2" s="58"/>
@@ -10549,13 +12121,13 @@
         <v>56</v>
       </c>
       <c r="D4" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="F4" s="31" t="s">
         <v>148</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>149</v>
       </c>
       <c r="G4" s="31" t="s">
         <v>57</v>
@@ -10566,10 +12138,10 @@
     </row>
     <row r="5" spans="2:8" ht="33.75" customHeight="1">
       <c r="B5" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D5" s="5">
         <v>3</v>
@@ -10590,10 +12162,10 @@
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1">
       <c r="B6" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D6" s="5">
         <v>3</v>
@@ -10614,10 +12186,10 @@
     </row>
     <row r="7" spans="2:8" ht="33.75" customHeight="1">
       <c r="B7" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D7" s="5">
         <v>4</v>
@@ -10638,10 +12210,10 @@
     </row>
     <row r="8" spans="2:8" ht="33.75" customHeight="1">
       <c r="B8" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>208</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>209</v>
       </c>
       <c r="D8" s="5">
         <v>4</v>
@@ -10662,10 +12234,10 @@
     </row>
     <row r="9" spans="2:8" ht="33.75" customHeight="1">
       <c r="B9" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="33" t="s">
         <v>210</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>211</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -10686,10 +12258,10 @@
     </row>
     <row r="10" spans="2:8" ht="33.75" customHeight="1">
       <c r="B10" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>212</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>213</v>
       </c>
       <c r="D10" s="5">
         <v>2</v>
@@ -10734,10 +12306,10 @@
     </row>
     <row r="12" spans="2:8" ht="33.75" customHeight="1">
       <c r="B12" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>214</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>215</v>
       </c>
       <c r="D12" s="5">
         <v>5</v>
@@ -10758,10 +12330,10 @@
     </row>
     <row r="14" spans="2:8" ht="118.7" customHeight="1">
       <c r="B14" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="65" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D14" s="66"/>
       <c r="E14" s="66"/>
@@ -10811,7 +12383,7 @@
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
       <c r="B2" s="60" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C2" s="58"/>
     </row>
@@ -10841,16 +12413,16 @@
       <c r="B6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>137</v>
+      <c r="C6" s="99" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30" customHeight="1">
       <c r="B7" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>217</v>
+      <c r="C7" s="99" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -10859,37 +12431,37 @@
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
       <c r="B9" s="75" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C9" s="76"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
       <c r="B10" s="70" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C10" s="69"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
       <c r="B11" s="70" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C11" s="69"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
       <c r="B12" s="70" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C12" s="69"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
       <c r="B13" s="70" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C13" s="69"/>
     </row>
     <row r="14" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B14" s="70" t="s">
-        <v>223</v>
+      <c r="B14" s="68" t="s">
+        <v>257</v>
       </c>
       <c r="C14" s="69"/>
     </row>
@@ -10899,25 +12471,25 @@
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
       <c r="B16" s="73" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C16" s="74"/>
     </row>
     <row r="17" spans="2:3" ht="25.5" customHeight="1">
       <c r="B17" s="68" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="C17" s="69"/>
     </row>
     <row r="18" spans="2:3" ht="25.5" customHeight="1">
       <c r="B18" s="68" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="C18" s="69"/>
     </row>
     <row r="19" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B19" s="70" t="s">
-        <v>227</v>
+      <c r="B19" s="68" t="s">
+        <v>260</v>
       </c>
       <c r="C19" s="69"/>
     </row>
@@ -10927,25 +12499,25 @@
     </row>
     <row r="21" spans="2:3" ht="15" customHeight="1">
       <c r="B21" s="71" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C21" s="72"/>
     </row>
     <row r="22" spans="2:3" ht="25.5" customHeight="1">
       <c r="B22" s="70" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C22" s="69"/>
     </row>
     <row r="23" spans="2:3" ht="25.5" customHeight="1">
       <c r="B23" s="68" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C23" s="69"/>
     </row>
     <row r="24" spans="2:3" ht="25.5" customHeight="1">
       <c r="B24" s="68" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C24" s="69"/>
     </row>
@@ -10996,7 +12568,7 @@
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
       <c r="B2" s="90" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C2" s="58"/>
       <c r="D2" s="58"/>
@@ -11012,7 +12584,7 @@
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
       <c r="B3" s="61" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="56"/>
@@ -11040,16 +12612,16 @@
         <v>67</v>
       </c>
       <c r="F4" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G4" s="31" t="s">
         <v>152</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>153</v>
       </c>
       <c r="H4" s="31" t="s">
         <v>68</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J4" s="31" t="s">
         <v>69</v>
@@ -11072,10 +12644,10 @@
         <v>71</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F5" s="23">
         <v>1</v>
@@ -11091,7 +12663,7 @@
         <v>100</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K5" s="21">
         <f t="shared" ref="K5:M19" si="1">IF(AND(K$4&gt;=$F5,K$4&lt;=$G5),1,"")</f>
@@ -11114,10 +12686,10 @@
         <v>71</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F6" s="23">
         <v>1</v>
@@ -11133,7 +12705,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K6" s="21">
         <f t="shared" si="1"/>
@@ -11156,10 +12728,10 @@
         <v>72</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F7" s="23">
         <v>1</v>
@@ -11175,7 +12747,7 @@
         <v>100</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K7" s="21">
         <f t="shared" si="1"/>
@@ -11198,10 +12770,10 @@
         <v>72</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F8" s="23">
         <v>1</v>
@@ -11217,7 +12789,7 @@
         <v>100</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K8" s="21">
         <f t="shared" si="1"/>
@@ -11240,10 +12812,10 @@
         <v>73</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F9" s="23">
         <v>2</v>
@@ -11259,7 +12831,7 @@
         <v>100</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K9" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11282,10 +12854,10 @@
         <v>73</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F10" s="23">
         <v>2</v>
@@ -11301,7 +12873,7 @@
         <v>100</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K10" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11324,10 +12896,10 @@
         <v>73</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F11" s="23">
         <v>2</v>
@@ -11343,7 +12915,7 @@
         <v>100</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K11" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11366,10 +12938,10 @@
         <v>73</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F12" s="23">
         <v>2</v>
@@ -11385,7 +12957,7 @@
         <v>100</v>
       </c>
       <c r="J12" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K12" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11408,10 +12980,10 @@
         <v>73</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F13" s="23">
         <v>2</v>
@@ -11427,7 +12999,7 @@
         <v>100</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K13" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11450,10 +13022,10 @@
         <v>73</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F14" s="23">
         <v>2</v>
@@ -11469,7 +13041,7 @@
         <v>100</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K14" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11492,10 +13064,10 @@
         <v>73</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F15" s="23">
         <v>2</v>
@@ -11511,7 +13083,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K15" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11534,10 +13106,10 @@
         <v>75</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F16" s="23">
         <v>3</v>
@@ -11553,7 +13125,7 @@
         <v>100</v>
       </c>
       <c r="J16" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K16" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11576,10 +13148,10 @@
         <v>74</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F17" s="23">
         <v>3</v>
@@ -11595,7 +13167,7 @@
         <v>70</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="K17" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11618,10 +13190,10 @@
         <v>76</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F18" s="41">
         <v>3</v>
@@ -11637,7 +13209,7 @@
         <v>100</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K18" s="24"/>
       <c r="L18" s="24"/>
@@ -11651,10 +13223,10 @@
         <v>77</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F19" s="23">
         <v>3</v>
@@ -11670,7 +13242,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K19" s="21" t="str">
         <f t="shared" si="1"/>
@@ -11693,7 +13265,7 @@
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
       <c r="B22" s="93" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C22" s="94"/>
     </row>
@@ -11957,18 +13529,18 @@
     </row>
     <row r="24" spans="2:3" ht="30" customHeight="1">
       <c r="B24" s="4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="30" customHeight="1">
       <c r="B25" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/00.StartCamp_6team_project/docs/03_3일차_팀프로젝트_실습기획서_SeoulMySoulMate_완성본.xlsx
+++ b/00.StartCamp_6team_project/docs/03_3일차_팀프로젝트_실습기획서_SeoulMySoulMate_완성본.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\StartCamp\team_project\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\tmp\00.StartCamp_6team_project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604A28E4-9141-4DC8-8417-AFA048E9DD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398D685E-F55C-4954-9817-11496032B395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="255">
   <si>
     <r>
       <rPr>
@@ -5313,67 +5313,79 @@
   </si>
   <si>
     <r>
-      <t>주요</t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선정</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기능들</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> : </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모든</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">결과
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>데이터</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여행</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5381,107 +5393,113 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용해서</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플래너</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광정보를</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날짜</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>통합</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제공할</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메모</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순서를</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SQLite</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5489,89 +5507,95 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>했다</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">저장
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t>. (</t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이미지</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전체</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> + </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위치</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> + </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위치별</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>혼잡도</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마커</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5579,125 +5603,133 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제공</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>클러스터와</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> ), </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>여행계획</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필터</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t>(</t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>날짜</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">구현
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> +</t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시간</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t>)</t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>과</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인증</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>함께</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소를</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코스</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5705,35 +5737,37 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선택할</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>커뮤니티</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋아요</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5741,30 +5775,38 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있음</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">구현
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어디</t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실시간</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5772,17 +5814,18 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가실</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5790,107 +5833,114 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>때</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>리뷰</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혼잡도</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>많이</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따릉이</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>찾아보시죠</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상권</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">…???? </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>저희</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">연결
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서비스에서는</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다크</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5898,53 +5948,56 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소별</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모드</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t>/</t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>본인</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온보딩</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>여행코스</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사이트</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5952,17 +6005,18 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전체에</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>음악</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -5970,35 +6024,38 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대해</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">구현
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>리뷰를</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>축제</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6006,17 +6063,18 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작성할</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>캘린더와</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6024,17 +6082,18 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교통</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6042,35 +6101,37 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있어서</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최적경로는</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사람들이</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이번</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6078,17 +6139,18 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>원하는</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>범위에서</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6096,218 +6158,1193 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>넓은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시야를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>전체지도에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한눈에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>각</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>컨텐츠가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위치한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여행을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광객</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찾는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시민</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원가입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공유하려는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이용자</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 6,518</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>커뮤니티</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CRUD·Soul Chat·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플래너</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프론트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빌드와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>핵심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스모크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통과</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비밀번호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>토큰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>환경변수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외부</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누락</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실패에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>폴백과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>캐시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처리</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서버</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플래너</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방문시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메모</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>삭제</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
@@ -6315,1637 +7352,372 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>혼잡도를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>볼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하여</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카카오맵</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>클러스터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선택의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>첫</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>단계가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>효율적으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이루어질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>해당</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서비스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용률</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>유지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>체류시간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>향상을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>음악이나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>코난</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기능</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>카테고리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키워드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필터와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>혼잡도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따릉이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상권</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라이트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>/</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>재미요소를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>챗봇이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>어떻게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>결과를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일관적으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>내뱉고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>답할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>없는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>질문에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대해서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>어떻게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대처를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>설계를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>했는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>얘기하기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어려웠던</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>느낀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>소감한마디</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> -&gt; </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>·</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">결과
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>여행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>플래너</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>날짜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온보딩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>·</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>메모</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순서를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> SQLite</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">저장
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마커</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>클러스터와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>필터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">구현
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인증</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>코스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>커뮤니티</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>좋아요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">구현
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실시간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서울</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>혼잡도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따릉이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상권</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">연결
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다크</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>온보딩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
@@ -7954,2452 +7726,22 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>음악</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">구현
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>축제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>캘린더와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>교통</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최적경로는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이번</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>범위에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제외</t>
-    </r>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서울</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>여행을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>준비하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광객</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주말</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>찾는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서울</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시민</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회원가입</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>없이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공유하려는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이용자</t>
-    </r>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서울</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>종</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 6,518</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>적재</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>커뮤니티</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> CRUD·Soul Chat·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>플래너</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실시간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>프론트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빌드와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>핵심</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> API </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>스모크</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>통과</t>
-    </r>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비밀번호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>세션</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>토큰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>해시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>저장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, API </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>키</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>환경변수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>외부</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> API </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>누락</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실패에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>폴백과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>캐시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>처리</t>
-    </r>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서버</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>저장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서울</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>여행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>플래너</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>날짜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방문시간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>메모</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>날짜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>삭제</t>
-    </r>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>카카오맵</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마커</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>클러스터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>카테고리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지역</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>키워드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>필터와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상세</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>연결</t>
-    </r>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실시간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>혼잡도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따릉이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상권</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>라이트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다크</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테마</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>온보딩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사이트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>음악</t>
-    </r>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>사용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>경험을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>생각해서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>진행했다…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">.  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>챗봇에서도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>검색</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>결과에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>캘린더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>당장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>싶을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있어서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>혼잡도도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보여줌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자치구에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>혼잡도를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보여줘서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>여행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>목적에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맞는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>적절하게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선택할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>플랜을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>짜는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>과정을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자연스럽게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이어나갈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>고민을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>많이했습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>.</t>
     </r>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -11069,6 +8411,10 @@
     <xf numFmtId="176" fontId="45" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -11123,13 +8469,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11144,14 +8499,26 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -11189,32 +8556,7 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11479,10 +8821,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="52"/>
+      <c r="C2" s="54"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="9" t="s">
@@ -11517,10 +8859,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="49"/>
+      <c r="C9" s="51"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -11571,28 +8913,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="51"/>
+      <c r="C17" s="53"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="54"/>
+      <c r="C18" s="56"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="49"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="47"/>
+      <c r="C20" s="49"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -11625,13 +8967,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -11723,46 +9065,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="49"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="51"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -11794,22 +9136,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="30" customHeight="1">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="62" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
     </row>
     <row r="3" spans="2:11" ht="28.35" customHeight="1">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="65"/>
     </row>
     <row r="4" spans="2:11" ht="35.65" customHeight="1">
       <c r="B4" s="29" t="s">
@@ -11878,9 +9220,7 @@
       <c r="F7" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="K7" s="98" t="s">
-        <v>261</v>
-      </c>
+      <c r="K7" s="46"/>
     </row>
     <row r="8" spans="2:11" ht="66" customHeight="1">
       <c r="B8" s="23" t="s">
@@ -11898,9 +9238,7 @@
       <c r="F8" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="K8" s="98" t="s">
-        <v>248</v>
-      </c>
+      <c r="K8" s="46"/>
     </row>
     <row r="9" spans="2:11" ht="66" customHeight="1">
       <c r="B9" s="23" t="s">
@@ -11918,9 +9256,7 @@
       <c r="F9" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="K9" s="98" t="s">
-        <v>249</v>
-      </c>
+      <c r="K9" s="46"/>
     </row>
     <row r="10" spans="2:11" ht="66" customHeight="1">
       <c r="B10" s="23" t="s">
@@ -11938,9 +9274,7 @@
       <c r="F10" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="K10" s="98" t="s">
-        <v>250</v>
-      </c>
+      <c r="K10" s="46"/>
     </row>
     <row r="11" spans="2:11" ht="66" customHeight="1">
       <c r="B11" s="23" t="s">
@@ -11958,9 +9292,7 @@
       <c r="F11" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="K11" s="98" t="s">
-        <v>251</v>
-      </c>
+      <c r="K11" s="46"/>
     </row>
     <row r="12" spans="2:11" ht="66" customHeight="1">
       <c r="B12" s="23" t="s">
@@ -11978,9 +9310,7 @@
       <c r="F12" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="K12" s="98" t="s">
-        <v>252</v>
-      </c>
+      <c r="K12" s="46"/>
     </row>
     <row r="13" spans="2:11" ht="66" customHeight="1">
       <c r="B13" s="23" t="s">
@@ -11998,9 +9328,7 @@
       <c r="F13" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="K13" s="98" t="s">
-        <v>253</v>
-      </c>
+      <c r="K13" s="46"/>
     </row>
     <row r="14" spans="2:11" ht="66" customHeight="1">
       <c r="B14" s="23" t="s">
@@ -12092,26 +9420,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="49"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="51"/>
     </row>
     <row r="4" spans="2:8" ht="31.5" customHeight="1">
       <c r="B4" s="31" t="s">
@@ -12332,14 +9660,14 @@
       <c r="B14" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="65" t="s">
-        <v>254</v>
-      </c>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="67"/>
+      <c r="C14" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -12382,16 +9710,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="58"/>
+      <c r="C2" s="60"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="49"/>
+      <c r="C3" s="51"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="19" t="s">
@@ -12413,16 +9741,16 @@
       <c r="B6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="99" t="s">
-        <v>255</v>
+      <c r="C6" s="47" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30" customHeight="1">
       <c r="B7" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="99" t="s">
-        <v>256</v>
+      <c r="C7" s="47" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -12430,99 +9758,107 @@
       <c r="C8" s="20"/>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="70" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="76"/>
+      <c r="C9" s="71"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="72" t="s">
         <v>217</v>
       </c>
-      <c r="C10" s="69"/>
+      <c r="C10" s="73"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="72" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="69"/>
+      <c r="C11" s="73"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="72" t="s">
         <v>219</v>
       </c>
-      <c r="C12" s="69"/>
+      <c r="C12" s="73"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="72" t="s">
         <v>220</v>
       </c>
-      <c r="C13" s="69"/>
+      <c r="C13" s="73"/>
     </row>
     <row r="14" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B14" s="68" t="s">
-        <v>257</v>
-      </c>
-      <c r="C14" s="69"/>
+      <c r="B14" s="74" t="s">
+        <v>251</v>
+      </c>
+      <c r="C14" s="73"/>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="73" t="s">
+      <c r="B16" s="78" t="s">
         <v>221</v>
       </c>
-      <c r="C16" s="74"/>
+      <c r="C16" s="79"/>
     </row>
     <row r="17" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B17" s="68" t="s">
-        <v>258</v>
-      </c>
-      <c r="C17" s="69"/>
+      <c r="B17" s="74" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="73"/>
     </row>
     <row r="18" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B18" s="68" t="s">
-        <v>259</v>
-      </c>
-      <c r="C18" s="69"/>
+      <c r="B18" s="74" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" s="73"/>
     </row>
     <row r="19" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B19" s="68" t="s">
-        <v>260</v>
-      </c>
-      <c r="C19" s="69"/>
+      <c r="B19" s="74" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="73"/>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
     </row>
     <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="71" t="s">
+      <c r="B21" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="C21" s="72"/>
+      <c r="C21" s="77"/>
     </row>
     <row r="22" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="72" t="s">
         <v>223</v>
       </c>
-      <c r="C22" s="69"/>
+      <c r="C22" s="73"/>
     </row>
     <row r="23" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B23" s="68" t="s">
+      <c r="B23" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="69"/>
+      <c r="C23" s="73"/>
     </row>
     <row r="24" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="74" t="s">
         <v>224</v>
       </c>
-      <c r="C24" s="69"/>
+      <c r="C24" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
@@ -12531,14 +9867,6 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12567,36 +9895,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="49"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="51"/>
     </row>
     <row r="4" spans="2:13" ht="25.5" customHeight="1">
       <c r="B4" s="44" t="s">
@@ -13258,72 +10586,72 @@
       </c>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="91" t="s">
+      <c r="B21" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="92"/>
+      <c r="C21" s="82"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="C22" s="94"/>
+      <c r="C22" s="84"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="96"/>
+      <c r="C23" s="86"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="81"/>
+      <c r="C24" s="90"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="83"/>
+      <c r="C25" s="92"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="85"/>
+      <c r="C26" s="94"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="86" t="s">
+      <c r="B27" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="87"/>
+      <c r="C27" s="96"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="89"/>
+      <c r="C28" s="98"/>
     </row>
     <row r="29" spans="2:13" ht="15" customHeight="1">
-      <c r="B29" s="78" t="s">
+      <c r="B29" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="79"/>
+      <c r="C29" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="K5:M17 K19:M19">
@@ -13364,16 +10692,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="58"/>
+      <c r="C2" s="60"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="49"/>
+      <c r="C3" s="51"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">
